--- a/mysite/books.xlsx
+++ b/mysite/books.xlsx
@@ -599,7 +599,12 @@
     <row r="3">
       <c r="A3" s="10" t="n"/>
       <c r="B3" s="10" t="n"/>
-      <c r="C3" s="15" t="inlineStr"/>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">meow meow
+</t>
+        </is>
+      </c>
       <c r="D3" s="15" t="n"/>
       <c r="E3" s="15" t="n"/>
       <c r="F3" s="15" t="n"/>
